--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_308_R31.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_308_R31.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9659</v>
+        <v>4.7351</v>
       </c>
       <c r="E2" t="n">
-        <v>3.618</v>
+        <v>3.8998</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3479</v>
+        <v>0.8353</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.2425</v>
+        <v>4.4581</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4439</v>
+        <v>3.3271</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.6864</v>
+        <v>1.131</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.5177</v>
+        <v>3.4898</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2156</v>
+        <v>3.6137</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.7334</v>
+        <v>-0.1239</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2753</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2283</v>
+        <v>-0.2866</v>
       </c>
       <c r="O2" t="n">
-        <v>0.047</v>
+        <v>1.2549</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4403</v>
+        <v>-0.2359</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7774</v>
+        <v>0.2166</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6629</v>
+        <v>-0.4525</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1444</v>
+        <v>-0.6468</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3584</v>
+        <v>0.4254</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2901</v>
+        <v>4.1306</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5892</v>
+        <v>2.7491</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7009</v>
+        <v>1.3815</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4581</v>
+        <v>-1.2425</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3271</v>
+        <v>0.4439</v>
       </c>
       <c r="I3" t="n">
-        <v>1.131</v>
+        <v>-1.6864</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4898</v>
+        <v>-1.5177</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6137</v>
+        <v>0.2156</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1239</v>
+        <v>-1.7334</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.2753</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2866</v>
+        <v>0.2283</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2549</v>
+        <v>0.047</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6808999999999999</v>
+        <v>1.605</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.094</v>
+        <v>0.9085</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5869</v>
+        <v>0.6965</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6468</v>
+        <v>2.1444</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4254</v>
+        <v>3.3584</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. MUSA</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9641</v>
+        <v>3.0546</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7347</v>
+        <v>0.7023</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7705</v>
+        <v>2.3523</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1801</v>
+        <v>-0.7376</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8593</v>
+        <v>-2.3806</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6792</v>
+        <v>1.643</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1347</v>
+        <v>-0.9054</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4928</v>
+        <v>-2.0832</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3581</v>
+        <v>1.1778</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9546</v>
+        <v>0.1679</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6335</v>
+        <v>-0.2974</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3211</v>
+        <v>0.4653</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7324</v>
+        <v>0.3488</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5637</v>
+        <v>0.2519</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1687</v>
+        <v>0.0969</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8197</v>
+        <v>1.3558</v>
       </c>
       <c r="W4" t="n">
-        <v>2.428</v>
+        <v>1.3558</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1878</v>
+        <v>2.7529</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1981</v>
+        <v>1.5118</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3859</v>
+        <v>1.2411</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7376</v>
+        <v>2.4609</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3806</v>
+        <v>-1.7718</v>
       </c>
       <c r="I5" t="n">
-        <v>1.643</v>
+        <v>4.2327</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9054</v>
+        <v>1.4998</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.0832</v>
+        <v>-1.371</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1778</v>
+        <v>2.8708</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1679</v>
+        <v>0.9611</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2974</v>
+        <v>-0.4008</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4653</v>
+        <v>1.3619</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5179</v>
+        <v>0.2045</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6484</v>
+        <v>0.0121</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1305</v>
+        <v>0.1924</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3558</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>D. MUSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5837</v>
+        <v>2.5054</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6115</v>
+        <v>3.276</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9722</v>
+        <v>-0.7705</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4609</v>
+        <v>0.1801</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7718</v>
+        <v>0.8593</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2327</v>
+        <v>-0.6792</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4998</v>
+        <v>1.1347</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.371</v>
+        <v>1.4928</v>
       </c>
       <c r="L6" t="n">
-        <v>2.8708</v>
+        <v>-0.3581</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9611</v>
+        <v>-0.9546</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4008</v>
+        <v>-0.6335</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3619</v>
+        <v>-0.3211</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9647</v>
+        <v>1.2738</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8883</v>
+        <v>1.1051</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0764</v>
+        <v>0.1687</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0.8197</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4794</v>
+        <v>-0.1194</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5954</v>
+        <v>-1.9926</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0748</v>
+        <v>1.8731</v>
       </c>
       <c r="G7" t="n">
         <v>0.9359</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5614</v>
+        <v>-0.0373</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6765</v>
+        <v>0.2794</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1151</v>
+        <v>-0.3167</v>
       </c>
       <c r="V7" t="n">
         <v>0.1418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8817</v>
+        <v>-0.3188</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2158</v>
+        <v>0.2128</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.666</v>
+        <v>-0.5315</v>
       </c>
       <c r="G8" t="n">
         <v>0.093</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.0354</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3734</v>
+        <v>0.0551</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2249</v>
+        <v>-0.0905</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9606</v>
+        <v>-1.0614</v>
       </c>
       <c r="E9" t="n">
         <v>-1.3091</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3485</v>
+        <v>0.2477</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0323</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0004</v>
+        <v>-0.1013</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3077</v>
+        <v>-1.8907</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3261</v>
+        <v>1.1466</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0184</v>
+        <v>-3.0373</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2657</v>
+        <v>0.3794</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4598</v>
+        <v>0.9414</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1941</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7159</v>
+        <v>1.1659</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7527</v>
+        <v>1.0923</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0368</v>
+        <v>0.0736</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4502</v>
+        <v>-0.7865</v>
       </c>
       <c r="N10" t="n">
-        <v>0.293</v>
+        <v>-0.1509</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1573</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3523</v>
+        <v>-0.6772</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3383</v>
+        <v>0.2126</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0141</v>
+        <v>-0.8898</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4665</v>
+        <v>-3.2166</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. CABOCLO</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6465</v>
+        <v>-2.6108</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7714</v>
+        <v>-2.562</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8751</v>
+        <v>-0.0488</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6714</v>
+        <v>-0.2657</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1872</v>
+        <v>-0.4598</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5158</v>
+        <v>0.1941</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.342</v>
+        <v>-0.7159</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9677</v>
+        <v>-0.7527</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6257</v>
+        <v>0.0368</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3294</v>
+        <v>0.4502</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2195</v>
+        <v>0.293</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8901</v>
+        <v>0.1573</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0249</v>
+        <v>0.0492</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0499</v>
+        <v>0.1024</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.025</v>
+        <v>-0.0532</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6083</v>
+        <v>-1.4665</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6805</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1443</v>
+        <v>-3.3688</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1283</v>
+        <v>-2.446</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2726</v>
+        <v>-0.9228</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3794</v>
+        <v>-0.2112</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9414</v>
+        <v>1.0333</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-1.2446</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1659</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0923</v>
+        <v>1.5096</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0736</v>
+        <v>-0.7127</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7865</v>
+        <v>-1.0081</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1509</v>
+        <v>-0.4762</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.5319</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6237</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.232</v>
+        <v>-3.7112</v>
       </c>
       <c r="R12" t="n">
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9307</v>
+        <v>0.7007</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8057</v>
+        <v>0.3266</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.125</v>
+        <v>0.3741</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.2166</v>
+        <v>-2.0026</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.2166</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>B. CABOCLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1683</v>
+        <v>-3.6999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3463</v>
+        <v>-1.5223</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.822</v>
+        <v>-2.1776</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2112</v>
+        <v>-0.6714</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0333</v>
+        <v>-2.1872</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2446</v>
+        <v>1.5158</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7969000000000001</v>
+        <v>-0.342</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5096</v>
+        <v>-0.9677</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7127</v>
+        <v>0.6257</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0081</v>
+        <v>-0.3294</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4762</v>
+        <v>-1.2195</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5319</v>
+        <v>0.8901</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8556</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.7112</v>
+        <v>-2.5515</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0988</v>
+        <v>-0.0286</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5737</v>
+        <v>0.2989</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4749</v>
+        <v>-0.3275</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0026</v>
+        <v>-1.6083</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1444</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="14">
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.361900000000002</v>
+        <v>4.108800000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9195</v>
+        <v>3.666400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4424000000000007</v>
+        <v>0.4425000000000003</v>
       </c>
       <c r="G14" t="n">
         <v>5.346700000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4089999999999991</v>
+        <v>-0.4089999999999994</v>
       </c>
       <c r="I14" t="n">
-        <v>5.7556</v>
+        <v>5.755599999999999</v>
       </c>
       <c r="J14" t="n">
         <v>4.527699999999999</v>
@@ -1525,10 +1525,10 @@
         <v>3.9761</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5515000000000002</v>
+        <v>0.5515000000000003</v>
       </c>
       <c r="M14" t="n">
-        <v>0.819</v>
+        <v>0.8189999999999998</v>
       </c>
       <c r="N14" t="n">
         <v>-4.385</v>
@@ -1546,16 +1546,16 @@
         <v>15.0772</v>
       </c>
       <c r="S14" t="n">
-        <v>2.319600000000001</v>
+        <v>3.0663</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8729</v>
+        <v>3.6198</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5532999999999998</v>
+        <v>-0.5535000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.623500000000001</v>
+        <v>-6.6235</v>
       </c>
       <c r="W14" t="n">
         <v>8.2766</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1039</v>
+        <v>4.7977</v>
       </c>
       <c r="E15" t="n">
-        <v>3.884</v>
+        <v>3.2943</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2199</v>
+        <v>1.5034</v>
       </c>
       <c r="G15" t="n">
         <v>2.4889</v>
@@ -1624,13 +1624,13 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>2.236</v>
+        <v>0.9298</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8812</v>
+        <v>0.2915</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3548</v>
+        <v>0.6383</v>
       </c>
       <c r="V15" t="n">
         <v>2.5387</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3894</v>
+        <v>2.962</v>
       </c>
       <c r="E16" t="n">
         <v>2.5578</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1685</v>
+        <v>0.4042</v>
       </c>
       <c r="G16" t="n">
         <v>1.2396</v>
@@ -1702,13 +1702,13 @@
         <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1498</v>
+        <v>0.7224</v>
       </c>
       <c r="T16" t="n">
         <v>0.4208</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.271</v>
+        <v>0.3016</v>
       </c>
       <c r="V16" t="n">
         <v>0.5361</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2725</v>
+        <v>2.5078</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7508</v>
+        <v>1.6944</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.8134</v>
       </c>
       <c r="G17" t="n">
         <v>0.6729000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7071</v>
+        <v>-0.4718</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.963</v>
+        <v>-0.0193</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7442</v>
+        <v>-0.4525</v>
       </c>
       <c r="V17" t="n">
         <v>2.5387</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7205</v>
+        <v>0.2168</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9464</v>
+        <v>0.1716</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2259</v>
+        <v>0.0452</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.147</v>
+        <v>0.0428</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9195</v>
+        <v>0.006</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2275</v>
+        <v>0.0368</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1782</v>
+        <v>0.0536</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.215</v>
+        <v>0.0168</v>
       </c>
       <c r="L18" t="n">
         <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9688</v>
+        <v>-0.0108</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7045</v>
+        <v>-0.0108</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2643</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.615</v>
+        <v>0.174</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1246</v>
+        <v>0.118</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.092</v>
+        <v>0.061</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0536</v>
+        <v>-1.0142</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1456</v>
+        <v>1.0752</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0428</v>
+        <v>-0.4715</v>
       </c>
       <c r="H19" t="n">
-        <v>0.006</v>
+        <v>0.0805</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0368</v>
+        <v>-0.5521</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0536</v>
+        <v>0.0902</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0168</v>
+        <v>0.6925</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0108</v>
+        <v>-0.5617</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0108</v>
+        <v>-0.612</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.0502</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1349</v>
+        <v>0.2104</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.0553</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1349</v>
+        <v>0.1551</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3714</v>
+        <v>-0.1559</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4079</v>
+        <v>0.0028</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7793</v>
+        <v>-0.1587</v>
       </c>
       <c r="G20" t="n">
-        <v>0.666</v>
+        <v>-1.147</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3313</v>
+        <v>-0.9195</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3346</v>
+        <v>-0.2275</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1443</v>
+        <v>-0.1782</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0707</v>
+        <v>-0.215</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5217000000000001</v>
+        <v>-0.9688</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2606</v>
+        <v>-0.7045</v>
       </c>
       <c r="O20" t="n">
-        <v>0.261</v>
+        <v>-0.2643</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4112</v>
+        <v>-0.2614</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2636</v>
+        <v>0.181</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1476</v>
+        <v>-0.4424</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1444</v>
+        <v>0.7886</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1444</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9727</v>
+        <v>-0.6352</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9579</v>
+        <v>0.054</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9852</v>
+        <v>-0.6892</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4715</v>
+        <v>0.666</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0805</v>
+        <v>0.3313</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5521</v>
+        <v>0.3346</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0902</v>
+        <v>0.1443</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6925</v>
+        <v>0.0707</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.0736</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5617</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.612</v>
+        <v>0.2606</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0502</v>
+        <v>0.261</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8232</v>
+        <v>0.1474</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8883</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.065</v>
+        <v>0.2377</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1303</v>
+        <v>-1.0123</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2087</v>
+        <v>-1.5625</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0784</v>
+        <v>0.5502</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3701</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7038</v>
+        <v>0.8217</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8417</v>
+        <v>0.4878</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1379</v>
+        <v>0.3339</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2755</v>
+        <v>-1.9559</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4597</v>
+        <v>-2.8135</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1842</v>
+        <v>0.8577</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4853</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6203</v>
+        <v>-0.3007</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3857</v>
+        <v>0.0318</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.006</v>
+        <v>-0.3325</v>
       </c>
       <c r="V23" t="n">
         <v>4.0052</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.336</v>
+        <v>-2.4038</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3144</v>
+        <v>-0.5503</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0216</v>
+        <v>-1.8536</v>
       </c>
       <c r="G24" t="n">
         <v>-2.804</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6427</v>
+        <v>-0.7106</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0272</v>
+        <v>-0.2631</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6155</v>
+        <v>-0.4474</v>
       </c>
       <c r="V24" t="n">
         <v>0.6468</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6705</v>
+        <v>-5.3851</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.922</v>
+        <v>-3.0963</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7485</v>
+        <v>-2.2888</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1788</v>
@@ -2404,13 +2404,13 @@
         <v>2.3195</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.5071</v>
+        <v>-1.2217</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4857</v>
+        <v>-0.6601</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0214</v>
+        <v>-0.5616</v>
       </c>
       <c r="V25" t="n">
         <v>-2.1444</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.362099999999998</v>
+        <v>-1.002899999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.262200000000001</v>
+        <v>-1.2619</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.1</v>
+        <v>0.2589999999999995</v>
       </c>
       <c r="G26" t="n">
         <v>-5.346499999999999</v>
@@ -2452,10 +2452,10 @@
         <v>0.4089999999999997</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.755699999999999</v>
+        <v>-5.7557</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8189000000000002</v>
+        <v>-0.8188999999999993</v>
       </c>
       <c r="K26" t="n">
         <v>4.385199999999999</v>
@@ -2482,13 +2482,13 @@
         <v>12.7575</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.3195</v>
+        <v>0.03950000000000009</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5533999999999999</v>
+        <v>0.5533999999999998</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.8731</v>
+        <v>-0.5138000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>6.623500000000001</v>
